--- a/02_DIA_inicio_2026_analisis_assets/rbd_9600_escuela-nanihue_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9600_escuela-nanihue_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82D53E22-F015-4169-864B-1F65A454A8A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC193AA7-67B1-4CFE-B0EB-ED8C59F9A15B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22807E72-51BB-4902-898B-EE82D5E4C780}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF9FE092-8F81-4F8B-88BD-DBF96B1B0EA7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0997D8D-58CC-4999-B73D-828952F87E82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38466CBB-6CB1-4538-9B5E-51FFAD76701B}"/>
 </file>